--- a/docs/TEM_TAPP_v7.xlsx
+++ b/docs/TEM_TAPP_v7.xlsx
@@ -2,23 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="94" yWindow="1509" windowWidth="21849" windowHeight="9951" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAPP'!$C$1:$N$93</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,36 +28,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000070C0"/>
+      <color rgb="FF0070C0"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="FF7030A0"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -68,27 +89,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -166,9 +187,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -527,49 +554,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AJ93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="4" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="30" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="30" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="15.3046875" customWidth="1" style="21" min="1" max="1"/>
+    <col width="32.921875" customWidth="1" style="21" min="2" max="2"/>
+    <col width="10.23046875" customWidth="1" style="21" min="3" max="3"/>
+    <col width="9.61328125" customWidth="1" style="21" min="4" max="4"/>
+    <col width="12.23046875" customWidth="1" style="21" min="5" max="5"/>
+    <col width="27.3828125" customWidth="1" style="21" min="6" max="6"/>
+    <col width="10.84375" customWidth="1" style="21" min="7" max="7"/>
+    <col hidden="1" width="14" customWidth="1" style="21" min="8" max="8"/>
+    <col width="8.3046875" customWidth="1" style="21" min="9" max="9"/>
+    <col width="7.765625" customWidth="1" style="21" min="10" max="10"/>
+    <col width="10.4609375" customWidth="1" style="21" min="11" max="11"/>
+    <col width="24.53515625" customWidth="1" style="21" min="12" max="12"/>
+    <col width="23.61328125" customWidth="1" style="21" min="13" max="13"/>
+    <col width="27" customWidth="1" style="21" min="14" max="14"/>
+    <col width="30" customWidth="1" style="21" min="15" max="33"/>
+    <col width="9.23046875" customWidth="1" style="21" min="34" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.55" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metadata Item</t>
@@ -625,17 +635,17 @@
           <t>Electron Diffraction</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>schema path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>matchComment</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>implementation notes</t>
         </is>
@@ -751,7 +761,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="1" ht="19.3" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>1. Protocol Identification</t>
@@ -779,6 +789,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
       <c r="O2" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -890,7 +903,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="1" ht="72.90000000000001" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Protocol Name</t>
@@ -942,16 +955,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:name</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:name is the short descriptive name for the method.</t>
         </is>
       </c>
+      <c r="N3" s="1" t="n"/>
       <c r="O3" s="9" t="n"/>
       <c r="P3" s="1" t="inlineStr">
         <is>
@@ -1059,7 +1073,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="1" ht="63.45" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Technique</t>
@@ -1111,20 +1125,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.schema:measurementTechnique.schema:DefinedTerm.schema:name</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:measurementTechnique.schema:DefinedTerm.schema:termCode</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:measurementTechnique is a DefinedTerm; use .schema:termCode for the controlled-list code</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>schema:DefinedTerm.schema:termCode
-datatype: enum {LA-ICP-MS | LA-ICP-OES | LA-MC-ICP-MS | LA-ICP-ToF-MS | LA-ICP-MS/MS | Other: specify}</t>
+datatype: string
+enum {TEM | STEM | TEM/STEM | Other: specify }
+read-only: True</t>
         </is>
       </c>
       <c r="O4" s="9" t="n"/>
@@ -1234,7 +1250,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1" ht="87.45" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Protocol Author</t>
@@ -1286,14 +1302,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:creator.schema:Person | schema.Organization.schema:name</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t>match. schema:creator is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: True
+DataType: string</t>
         </is>
       </c>
       <c r="O5" s="9" t="n"/>
@@ -1403,7 +1425,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="78.55" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Laboratory</t>
@@ -1455,14 +1477,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:location.scheme:Place.schema:name</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>match. ada:laboratory extends spatialExtent (schema:Place); schema:name is the lab/facility name.</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: False
+DataType: string</t>
         </is>
       </c>
       <c r="O6" s="9" t="n"/>
@@ -1572,7 +1600,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="58.3" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Laboratory ID</t>
@@ -1624,14 +1652,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:location.scheme:Place.schema:identifier</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="1" t="inlineStr">
         <is>
           <t>match. schema:Place schema:identifier (ROR or other PID) on ada:laboratory.</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: False
+DataType: string  format: uri</t>
         </is>
       </c>
       <c r="O7" s="9" t="n"/>
@@ -1741,7 +1775,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" ht="102" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Protocol Start Date</t>
@@ -1793,14 +1827,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:datePublished</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="1" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:datePublished is explicitly described as 'ISO 8601 date when this method configuration was first used'.</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: True
+DataType: Date</t>
         </is>
       </c>
       <c r="O8" s="9" t="n"/>
@@ -1910,7 +1950,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" ht="145.75" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Protocol Development</t>
@@ -1962,19 +2002,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:funding[].schema:MonetaryGrant.schema:name</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>match. schema:funding[] is an array of MonetaryGrant; also has schema:identifier (award number) and schema:funder (organisation).</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>put text in MonetaryGrant name unless can clearly parse identifier distinct from name.</t>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>schema:funding[] is an array of MonetaryGrant; also has schema:identifier (award number) and schema:funder (organisation). put text in MonetaryGrant name unless can clearly parse identifier distinct from name.</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>read-only:True</t>
         </is>
       </c>
       <c r="O9" s="9" t="n"/>
@@ -2084,7 +2124,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" ht="131.15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Protocol Reference(s)</t>
@@ -2136,19 +2176,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'techniquePublication'].</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>match. schema:relatedLink[] is a labeledLink with schema:url and schema:name; fits DOIs/URLs of method publications.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>target URL to publication , target name should be title of publication</t>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>schema:relatedLink[] is a labeledLink with schema:url and schema:name; fits DOIs/URLs of method publications. target URL to publication , target name should be title of publication</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>read-only:True</t>
         </is>
       </c>
       <c r="O10" s="9" t="n"/>
@@ -2258,7 +2298,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1" ht="65.15000000000001" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Protocol DOI</t>
@@ -2310,9 +2350,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.schema:identifier</t>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>$Dataset.schema:measuremntTechnique.schema:DefinedTerm.schema.name and schema.identifier</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>This should be the identifier for the protocol definition that the analysis level 'detail' is extenting for a particular dataset.</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>required</t>
         </is>
       </c>
       <c r="O11" s="9" t="n"/>
@@ -2422,7 +2472,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1" ht="102" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Analyst</t>
@@ -2474,11 +2524,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:Agent/schema:Person.schema:name, schema:identifier</t>
         </is>
       </c>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -2586,7 +2638,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1" ht="29.15" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Analysis Start Date</t>
@@ -2638,11 +2690,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:startDate</t>
         </is>
       </c>
+      <c r="M13" s="1" t="n"/>
+      <c r="N13" s="1" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="1" t="inlineStr">
         <is>
@@ -2750,7 +2804,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1" ht="43.75" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Analysis End Date</t>
@@ -2802,11 +2856,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:endDate</t>
         </is>
       </c>
+      <c r="M14" s="1" t="n"/>
+      <c r="N14" s="1" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="1" t="inlineStr">
         <is>
@@ -2914,7 +2970,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1" ht="41.25" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Analysis</t>
@@ -2966,11 +3022,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>$Dataset.schema:funding</t>
         </is>
       </c>
+      <c r="M15" s="1" t="n"/>
+      <c r="N15" s="1" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="1" t="inlineStr">
         <is>
@@ -3078,7 +3136,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="79.84999999999999" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Coupled Technique(s)</t>
@@ -3130,20 +3188,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:name</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="1" t="inlineStr">
         <is>
           <t>range should be analytical technique vocabulary</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>schema:DefinedTerm.schema:termCode
-datatype: enum {EPMA | SIMS | ICP-MS (solution) | Noble Gas MS | Other: specify | None}</t>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O16" s="9" t="n"/>
@@ -3253,7 +3311,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="131.25" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Coupling Description</t>
@@ -3305,17 +3363,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:description</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>386</v>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" s="1" t="inlineStr">
         <is>
           <t>text description of relationship</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O17" s="9" t="n"/>
@@ -3425,7 +3486,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1" ht="72.90000000000001" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Coupled Protocol DOI</t>
@@ -3477,11 +3538,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:url</t>
         </is>
       </c>
+      <c r="M18" s="1" t="n"/>
+      <c r="N18" s="1" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="1" t="inlineStr">
         <is>
@@ -3589,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1" ht="116.6" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Coupled Dataset or Publication Reference</t>
@@ -3641,11 +3704,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledDataset'].schema:target</t>
         </is>
       </c>
+      <c r="M19" s="1" t="n"/>
+      <c r="N19" s="1" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
@@ -3753,7 +3818,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
@@ -3765,6 +3830,9 @@
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
+      <c r="L20" s="1" t="n"/>
+      <c r="M20" s="1" t="n"/>
+      <c r="N20" s="1" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="1" t="n"/>
       <c r="Q20" s="1" t="n"/>
@@ -3820,7 +3888,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2. Samples</t>
@@ -3848,6 +3916,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L21" s="1" t="n"/>
+      <c r="M21" s="1" t="n"/>
+      <c r="N21" s="1" t="n"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3959,7 +4030,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1" ht="121.3" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Target Material</t>
@@ -4011,20 +4082,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:object[].schema:DefinedTerm.schema.name</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="1" t="inlineStr">
         <is>
           <t>match. schema:object[] is an array of DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary or target materials…</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="1" t="inlineStr">
         <is>
           <t>schema:DefinedTerm.schema:termCode
-datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify}</t>
+datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify}
+read-only:True</t>
         </is>
       </c>
       <c r="O22" s="9" t="n"/>
@@ -4134,7 +4206,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" ht="204" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Sample Preparation Method</t>
@@ -4186,19 +4258,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:description</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:additionalType='samplePreparation'].schema:name</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
         <is>
           <t>Sample preparation is a dedicated step (typically schema:position=1) in the actionProcess; schema:object is input, mostly likely the original sample. Schema:result is the product that will be used directly for analysis, e.g. polished thin section or epoxy mount; describe procedure in schema:step/schema:description</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>property:samplePreparationMethodDefault dataType: string readOnly: False</t>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>property:samplePreparationMethod
+ dataType: string 
+readOnly: True
+enum: {FIB lift-out (Ga ion) | FIB lift-out (Xe plasma) | FIB lift-out (Ga) + ion mill | Ultramicrotomy | Crushing / dispersion on grid | Ion milling (non-FIB) | Electropolishing | Other: specify | Unknown}</t>
         </is>
       </c>
       <c r="O23" s="9" t="n"/>
@@ -4308,7 +4383,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="169.3" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Sample Preparation Details</t>
@@ -4360,6 +4435,18 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:additionalType='samplePreparation'].schema:description</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="n"/>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
+        </is>
+      </c>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="1" t="inlineStr">
         <is>
@@ -4467,7 +4554,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" ht="114" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Sample Name</t>
@@ -4519,11 +4606,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="1" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:object[@type ="schema:Thing",            "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:name</t>
         </is>
       </c>
+      <c r="M25" s="1" t="n"/>
+      <c r="N25" s="1" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="1" t="inlineStr">
         <is>
@@ -4631,7 +4720,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" ht="102" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Sample Persistent Identifier</t>
@@ -4683,11 +4772,13 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:identifier</t>
         </is>
       </c>
+      <c r="M26" s="1" t="n"/>
+      <c r="N26" s="1" t="n"/>
       <c r="O26" s="9" t="n"/>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -4795,7 +4886,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
@@ -4807,6 +4898,9 @@
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
+      <c r="L27" s="1" t="n"/>
+      <c r="M27" s="1" t="n"/>
+      <c r="N27" s="1" t="n"/>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="1" t="n"/>
       <c r="Q27" s="1" t="n"/>
@@ -4862,7 +4956,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" ht="29.15" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>3. Instrument &amp; Software</t>
@@ -4890,6 +4984,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L28" s="1" t="n"/>
+      <c r="M28" s="1" t="n"/>
+      <c r="N28" s="1" t="n"/>
       <c r="O28" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5001,7 +5098,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" ht="87.45" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Instrument Manufacturer</t>
@@ -5053,14 +5150,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="1" t="inlineStr">
         <is>
           <t>match. CDIF instrument inherits schema.org Product's schema:manufacturer.</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>read-only: True
+dataType: string
+enum: {JEOL | ThermoFisher Scientific (FEI) | Hitachi | Nion | Zeiss | Other: specify | Unknown }</t>
         </is>
       </c>
       <c r="O29" s="9" t="n"/>
@@ -5170,7 +5274,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" ht="87.45" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Instrument Model</t>
@@ -5222,14 +5326,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:model.schema:name</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="1" t="inlineStr">
         <is>
           <t>match. CDIF instrument inherits schema.org Product's schema:model.</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>READ-only: irue
+dataType: string</t>
         </is>
       </c>
       <c r="O30" s="9" t="n"/>
@@ -5339,7 +5449,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" ht="145.75" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Electron Source</t>
@@ -5391,14 +5501,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'ElectronSource'</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ElectronSource'].schema:name</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
         <is>
           <t>match. Electron source/gun modelled as a sub-component of the instrument via schema:hasPart[]; classify the part via schema:additionalType (e.g. 'ElectronGun:FEG') and carry the label in schema:name.</t>
+        </is>
+      </c>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>read-only: True
+dataType: string
+enum: {Cold-FEG | Schottky FEG (X-FEG) | Schottky FEG (standard) | LaB6 / CeB6 | Tungsten (W) | Other: specify | Unknown  }</t>
         </is>
       </c>
       <c r="O31" s="9" t="n"/>
@@ -5508,7 +5625,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1" ht="94.75" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Aberration Corrector</t>
@@ -5560,6 +5677,19 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'AberrationCorrector'].schema:name</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="n"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>read-only: True
+dataType: string
+enum: {None | Probe Cs-corrected (STEM) | Image Cs-corrected (TEM) | Both probe and image corrected | Cs-corrected (type unknown) | Other: specify | Unknown }</t>
+        </is>
+      </c>
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="1" t="inlineStr">
         <is>
@@ -5667,7 +5797,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" ht="72.90000000000001" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Monochromator</t>
@@ -5721,6 +5851,23 @@
       <c r="K33" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'Monochromator'].schema:name</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>read-only: True
+dataType: string
+enum: {Yes - active | Yes - not used | No | Unknown }</t>
         </is>
       </c>
       <c r="O33" s="9" t="n"/>
@@ -5830,7 +5977,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="87.45" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Sample Holder</t>
@@ -5882,6 +6029,19 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'SampleHolder'].schema:name</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="n"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>read-only: False
+dataType: string
+enum: {Yes - active | Yes - not used | No | Unknown }</t>
+        </is>
+      </c>
       <c r="O34" s="9" t="n"/>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -5989,7 +6149,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="66.90000000000001" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Spectroscopic Detector(s)</t>
@@ -6043,6 +6203,23 @@
       <c r="K35" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'SpectroscopicDetector'].schema:name</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>read-only: False
+dataType: string
+enum: {EDS only | EELS only | EDS and EELS | EELS and EFTEM | EDS and EELS and EFTEM | None }</t>
         </is>
       </c>
       <c r="O35" s="9" t="n"/>
@@ -6152,7 +6329,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1" ht="174.9" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>EDS Detector Configuration</t>
@@ -6208,19 +6385,21 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'edsDetector'</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Match as sub-component. EDS detector as a hasPart with schema:manufacturer, schema:model, and schema:description capturing window type, pulse-processor, detector area.</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>schema:additional type = 'EDS detector'</t>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'edsDetector']</t>
+        </is>
+      </c>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'
+Match as sub-component. EDS detector as a hasPart with schema:manufacturer, schema:model, and schema:description</t>
+        </is>
+      </c>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>read-only: True
+dataType: string</t>
         </is>
       </c>
       <c r="O36" s="9" t="n"/>
@@ -6330,7 +6509,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" ht="160.3" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>EELS Spectrometer</t>
@@ -6384,6 +6563,22 @@
       <c r="K37" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'eelsSpectrometer']</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: True
+dataType: string</t>
         </is>
       </c>
       <c r="O37" s="9" t="n"/>
@@ -6493,7 +6688,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="1" ht="102" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Imaging and Diffraction Detectors</t>
@@ -6545,6 +6740,18 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ImagingAndDiffractionDetector']</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="n"/>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: True
+dataType: string</t>
+        </is>
+      </c>
       <c r="O38" s="9" t="n"/>
       <c r="P38" s="1" t="inlineStr">
         <is>
@@ -6652,7 +6859,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1" ht="114.9" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Detector</t>
@@ -6706,6 +6913,22 @@
       <c r="K39" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'STEM4Ddetector']</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>Read-only: True
+dataType: string</t>
         </is>
       </c>
       <c r="O39" s="9" t="n"/>
@@ -6815,7 +7038,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="68.15000000000001" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Acquisition Software</t>
@@ -6867,19 +7090,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.bios:computationalTool[]</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>match. bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>toolRole = acquisition</t>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>toolRole = acquisition
+read-only: False
+dataType: string</t>
         </is>
       </c>
       <c r="O40" s="9" t="n"/>
@@ -6989,7 +7214,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="59.6" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>SAED Pattern Simulation Software</t>
@@ -7043,6 +7268,23 @@
       <c r="K41" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.bios:computationalTool[]</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>toolRole = processing
+read-only: False
+dataType: string</t>
         </is>
       </c>
       <c r="O41" s="9" t="n"/>
@@ -7152,7 +7394,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="131.15" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>Data Reduction Software</t>
@@ -7204,19 +7446,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>$MethodDefinition.bios:computationalTool[]</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>toolRole = data reduction</t>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t>ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>toolRole = data reduction
+read-only: False
+dataType: string</t>
         </is>
       </c>
       <c r="O42" s="9" t="n"/>
@@ -7326,7 +7570,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
@@ -7338,6 +7582,9 @@
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
+      <c r="L43" s="1" t="n"/>
+      <c r="M43" s="1" t="n"/>
+      <c r="N43" s="1" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="n"/>
@@ -7393,7 +7640,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1" ht="29.15" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>4. Measurement Information</t>
@@ -7421,6 +7668,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L44" s="1" t="n"/>
+      <c r="M44" s="1" t="n"/>
+      <c r="N44" s="1" t="n"/>
       <c r="O44" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7532,7 +7782,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1" ht="63" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Analytical Mode</t>
@@ -7558,9 +7808,9 @@
           <t>Controlled vocabulary</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>'TEM Imaging' | 'STEM Imaging' | 'Electron Diffraction' | 'STEM Imaging; Electron Diffraction'</t>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>TEM Imaging' | 'STEM Imaging' | 'Electron Diffraction' | 'STEM Imaging; Electron Diffraction'</t>
         </is>
       </c>
       <c r="G45" s="1" t="n"/>
@@ -7584,9 +7834,18 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>property:analyticalMode dataType: string readOnly: True enum {Spot | Transect | Mapping | Spot; Transect}</t>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:analyticalMode[]</t>
+        </is>
+      </c>
+      <c r="M45" s="1" t="n"/>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>property:analyticalMode
+ dataType: string 
+read-Only: True
+ enum {'TEM Imaging' | 'STEM Imaging' | 'Electron Diffraction' | 'STEM Imaging; Electron Diffraction'}</t>
         </is>
       </c>
       <c r="O45" s="9" t="inlineStr">
@@ -7616,7 +7875,7 @@
       <c r="AI45" s="1" t="n"/>
       <c r="AJ45" s="1" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="50.6" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>Accelerating Voltage</t>
@@ -7670,6 +7929,24 @@
       <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:acceleratingVoltage</t>
+        </is>
+      </c>
+      <c r="M46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> schema:unitText='kV'</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">property:  acceleratingVoltage
+  datatype: string
+  readonly: False 
+</t>
         </is>
       </c>
       <c r="O46" s="9" t="n"/>
@@ -7779,7 +8056,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="121.3" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Analytical Sub-mode</t>
@@ -7831,6 +8108,24 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:analyticalMode[]</t>
+        </is>
+      </c>
+      <c r="M47" s="1" t="inlineStr">
+        <is>
+          <t>add to analyticalMode list.</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>property:analyticalMode
+ dataType: string 
+read-Only: False
+ enum {BF-TEM | DF-TEM | HRTEM | EFTEM (TEM Imaging); HAADF | ABF | BF-STEM | ADF | MAADF (STEM Imaging); SAED | CBED | Nanobeam diffraction | Precession ED | 4D-STEM (Electron Diffraction) | Other: specify}</t>
+        </is>
+      </c>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="1" t="inlineStr">
         <is>
@@ -7938,7 +8233,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="116.6" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>TEM Objective Aperture</t>
@@ -7992,6 +8287,22 @@
       <c r="K48" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'TEM Objective Aperture',  schema.value</t>
+        </is>
+      </c>
+      <c r="M48" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O48" s="9" t="n"/>
@@ -8101,7 +8412,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="87.45" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>EFTEM Energy Window</t>
@@ -8155,6 +8466,22 @@
       <c r="K49" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EFTEM Energy Window'  , schema.value</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O49" s="9" t="n"/>
@@ -8264,7 +8591,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="61.3" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>HAADF Collection Angles</t>
@@ -8318,6 +8645,22 @@
       <c r="K50" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'HAADF Collection Angles' , schema.value</t>
+        </is>
+      </c>
+      <c r="M50" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O50" s="9" t="n"/>
@@ -8427,7 +8770,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" ht="79.75" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>Convergence Semi-Angle</t>
@@ -8481,6 +8824,21 @@
       <c r="K51" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:convergenceSemiAngle</t>
+        </is>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'  or ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>property: convergenceSemiAngle datatype: string readOnly: True</t>
         </is>
       </c>
       <c r="O51" s="9" t="n"/>
@@ -8590,7 +8948,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="71.15000000000001" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>STEM Probe Diameter</t>
@@ -8644,6 +9002,22 @@
       <c r="K52" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Probe Diameter' , schema.value</t>
+        </is>
+      </c>
+      <c r="M52" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O52" s="9" t="n"/>
@@ -8753,7 +9127,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="87.45" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>STEM Probe Current</t>
@@ -8807,6 +9181,22 @@
       <c r="K53" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Probe Current' , schema.value</t>
+        </is>
+      </c>
+      <c r="M53" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O53" s="9" t="n"/>
@@ -8916,7 +9306,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="56.15" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>STEM Dwell Time per Pixel</t>
@@ -8970,6 +9360,23 @@
       <c r="K54" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:stemDwellTimePerPixel</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>property:stemDwellTimePerPixel
+ dataType: string 
+read-Only: False</t>
         </is>
       </c>
       <c r="O54" s="9" t="n"/>
@@ -9079,7 +9486,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="58.3" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>STEM Scan Dimensions</t>
@@ -9133,6 +9540,22 @@
       <c r="K55" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Scan Dimensions' , schema.value</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O55" s="9" t="n"/>
@@ -9242,7 +9665,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="72.90000000000001" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>STEM Frame Averaging</t>
@@ -9296,6 +9719,22 @@
       <c r="K56" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Frame Averaging' , schema.value</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O56" s="9" t="n"/>
@@ -9405,7 +9844,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="56.6" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>Camera Length</t>
@@ -9459,6 +9898,23 @@
       <c r="K57" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:cameraLength</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'STEM Imaging'  or ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>property:cameraLength
+ dataType: string 
+read-Only: False</t>
         </is>
       </c>
       <c r="O57" s="9" t="n"/>
@@ -9568,7 +10024,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="72.90000000000001" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Selected-Area Aperture Size</t>
@@ -9622,6 +10078,22 @@
       <c r="K58" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Selected-Area Aperture Size' , schema.value</t>
+        </is>
+      </c>
+      <c r="M58" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O58" s="9" t="n"/>
@@ -9731,7 +10203,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="53.6" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>Precession Angle</t>
@@ -9785,6 +10257,22 @@
       <c r="K59" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Precession Angle' , schema.value</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O59" s="9" t="n"/>
@@ -9894,7 +10382,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="72.90000000000001" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Scan Grid and Area</t>
@@ -9948,6 +10436,22 @@
       <c r="K60" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Scan Grid and Area' , schema.value</t>
+        </is>
+      </c>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O60" s="9" t="n"/>
@@ -10057,7 +10561,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="50.15" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Dwell Time per Probe Position</t>
@@ -10111,6 +10615,22 @@
       <c r="K61" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Dwell Time per Probe Position' , schema.value</t>
+        </is>
+      </c>
+      <c r="M61" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O61" s="9" t="n"/>
@@ -10220,7 +10740,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="131.15" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Diffraction Camera Length Calibration Method</t>
@@ -10274,6 +10794,22 @@
       <c r="K62" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Diffraction Camera Length Calibration Method' , schema.value</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O62" s="9" t="n"/>
@@ -10383,7 +10919,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="72" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>EDS Acquisition Mode</t>
@@ -10437,6 +10973,24 @@
       <c r="K63" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:edsAcquisitionMode</t>
+        </is>
+      </c>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>property:edsAcquisitionMode
+ dataType: string 
+read-Only: False
+enum: {Point analysis | Line scan | Spectrum image (map) | Simultaneous EDS+EELS | Other: specify}</t>
         </is>
       </c>
       <c r="O63" s="9" t="n"/>
@@ -10546,7 +11100,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="53.6" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>EDS Live Time per Point or Pixel</t>
@@ -10600,6 +11154,22 @@
       <c r="K64" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L64" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Live Time per Point or Pixel' , schema.value</t>
+        </is>
+      </c>
+      <c r="M64" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O64" s="9" t="n"/>
@@ -10709,7 +11279,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="72.90000000000001" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>EDS Energy Range</t>
@@ -10763,6 +11333,22 @@
       <c r="K65" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L65" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Energy Range' , schema.value</t>
+        </is>
+      </c>
+      <c r="M65" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O65" s="9" t="n"/>
@@ -10872,7 +11458,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="1" ht="96" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>EDS Quantification Method</t>
@@ -10926,6 +11512,24 @@
       <c r="K66" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L66" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:edsQuantificationMethod</t>
+        </is>
+      </c>
+      <c r="M66" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>property:edsQuantificationMethod
+ dataType: string 
+read-Only: True
+enum: {Cliff-Lorimer (k-factor) | ζ-factor (zeta-factor) | Absorption-corrected Cliff-Lorimer | Standardless | Direct comparison to reference spectra |  None}</t>
         </is>
       </c>
       <c r="O66" s="9" t="n"/>
@@ -11035,7 +11639,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>Analyte</t>
@@ -11091,14 +11695,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>$MethodDefinition.ada:analytes</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>list of target analytes</t>
+      <c r="L67" s="1" t="inlineStr">
+        <is>
+          <t>special handling</t>
+        </is>
+      </c>
+      <c r="M67" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">use to generate the default analytes list using the analyteTemplate; </t>
         </is>
       </c>
       <c r="O67" s="9" t="n"/>
@@ -11208,7 +11817,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="88.75" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>EELS Acquisition Mode</t>
@@ -11262,6 +11871,24 @@
       <c r="K68" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L68" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:eelsAcquisitionMode</t>
+        </is>
+      </c>
+      <c r="M68" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>property:eelsAcquisitionMode
+ dataType: string 
+read-Only: False
+enum: {Point spectrum | Line scan | Spectrum image (SI) | Dual-EELS (simultaneous low- and high-loss) | Simultaneous EDS+EELS | Other: specify | None}</t>
         </is>
       </c>
       <c r="O68" s="9" t="n"/>
@@ -11371,7 +11998,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="81" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>EELS Edges</t>
@@ -11425,6 +12052,23 @@
       <c r="K69" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:eelsEdges[]</t>
+        </is>
+      </c>
+      <c r="M69" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>property:eelsEdges
+ dataType: list of string 
+read-Only: False</t>
         </is>
       </c>
       <c r="O69" s="9" t="n"/>
@@ -11534,7 +12178,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="1" ht="72.90000000000001" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>EELS Collection Semi-Angle</t>
@@ -11588,6 +12232,23 @@
       <c r="K70" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L70" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:eelsCollectionSemiAngle</t>
+        </is>
+      </c>
+      <c r="M70" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>property:eelsCollectionSemiAngle
+ dataType: string 
+read-Only: True</t>
         </is>
       </c>
       <c r="O70" s="9" t="n"/>
@@ -11697,7 +12358,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="1" ht="58.3" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Dispersion</t>
@@ -11751,6 +12412,22 @@
       <c r="K71" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L71" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Dispersion' , schema.value</t>
+        </is>
+      </c>
+      <c r="M71" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: True</t>
         </is>
       </c>
       <c r="O71" s="9" t="n"/>
@@ -11860,7 +12537,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1" ht="67.3" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Resolution</t>
@@ -11914,6 +12591,22 @@
       <c r="K72" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L72" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Resolution' , schema.value</t>
+        </is>
+      </c>
+      <c r="M72" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: True</t>
         </is>
       </c>
       <c r="O72" s="9" t="n"/>
@@ -12023,7 +12716,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="72.90000000000001" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>EELS Acquisition Time per Spectrum</t>
@@ -12077,6 +12770,23 @@
       <c r="K73" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L73" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:eelsAcquisitionTimePerSpectrum</t>
+        </is>
+      </c>
+      <c r="M73" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>property:eelsAcquisitionTimePerSpectrum
+ dataType: string 
+read-Only: false</t>
         </is>
       </c>
       <c r="O73" s="9" t="n"/>
@@ -12186,7 +12896,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="87.45" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Loss Range</t>
@@ -12240,6 +12950,23 @@
       <c r="K74" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L74" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:eelsEnergyLossRange</t>
+        </is>
+      </c>
+      <c r="M74" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>property:eelsEnergyLossRange
+ dataType: string 
+read-Only: false</t>
         </is>
       </c>
       <c r="O74" s="9" t="n"/>
@@ -12349,7 +13076,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="n"/>
@@ -12361,6 +13088,9 @@
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
+      <c r="L75" s="1" t="n"/>
+      <c r="M75" s="1" t="n"/>
+      <c r="N75" s="1" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="1" t="n"/>
       <c r="Q75" s="1" t="n"/>
@@ -12416,7 +13146,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="1" ht="29.15" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>5. Data Processing</t>
@@ -12444,6 +13174,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L76" s="1" t="n"/>
+      <c r="M76" s="1" t="n"/>
+      <c r="N76" s="1" t="n"/>
       <c r="O76" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -12555,7 +13288,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="1" ht="102" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>Phase Identification Method</t>
@@ -12607,6 +13340,20 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:phaseIdentificatonMethod</t>
+        </is>
+      </c>
+      <c r="M77" s="1" t="n"/>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>property:phaseIdentificatonMethod
+ dataType: string 
+read-Only: True
+enum: {Manual d-spacing comparison to ICDD PDF database | JEMS simulation | CrystalMaker | WinHREM | py4DSTEM ACOM | ESPRIT CRYSTAL | ORIX | Other: specify | None}</t>
+        </is>
+      </c>
       <c r="O77" s="9" t="n"/>
       <c r="P77" s="1" t="inlineStr">
         <is>
@@ -12714,7 +13461,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="1" ht="102" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Orientation Mapping Method</t>
@@ -12768,6 +13515,22 @@
       <c r="K78" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L78" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Orientation Mapping Method' , schema.value</t>
+        </is>
+      </c>
+      <c r="M78" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: True</t>
         </is>
       </c>
       <c r="O78" s="9" t="n"/>
@@ -12877,7 +13640,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="72.90000000000001" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>EELS Background Subtraction Method</t>
@@ -12931,6 +13694,22 @@
       <c r="K79" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Background Subtraction Method' , schema.value</t>
+        </is>
+      </c>
+      <c r="M79" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O79" s="9" t="n"/>
@@ -13040,7 +13819,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="87.45" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>EELS Plural Scattering Correction</t>
@@ -13094,6 +13873,22 @@
       <c r="K80" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Plural Scattering Correction' , schema.value</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O80" s="9" t="n"/>
@@ -13203,7 +13998,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="1" ht="174.9" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>EDS Spectral Processing Type</t>
@@ -13211,7 +14006,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Method used to process EDS spectra and extract net peak intensities from raw spectral data. Applied before quantification (EDS Quantification Method). Common approaches include background fitting and subtraction followed by peak integration, and filter fit or Gaussian deconvolution for overlapping peaks.</t>
+          <t>Method used to process EDS spectra and extract net peak intensities from raw spectral data. Applied before quantification (EDS Quantification Method). Common approaches include background fitting and subtraction followed by peak integration, and filter fit or Gaussian deconvolution for overlapping peaks. Ideally should be a property on a workflow step associated with the software doing the processing.</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -13259,21 +14054,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>$.ada:methodParameters[]</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Direct match. Method-level parameter with ada:enumeration of EDS spectral processing modes.</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>parameter: edsSpectralProcessingType
-   datatype: enum {Background fitting | Peak deconvolution | Top hat | Gaussian | Filter fit | Other | Unknown}
-   readOnly: true</t>
+      <c r="L81" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Spectral Processing Type' , schema.value</t>
+        </is>
+      </c>
+      <c r="M81" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: True</t>
         </is>
       </c>
       <c r="O81" s="9" t="n"/>
@@ -13383,7 +14177,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="116.6" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Image Processing Methods Applied</t>
@@ -13391,7 +14185,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Image processing steps applied to TEM or STEM images during or after acquisition. Non-linear processing steps that could affect quantitative interpretation should be documented explicitly.</t>
+          <t>Image processing steps applied to TEM or STEM images during or after acquisition. Non-linear processing steps that could affect quantitative interpretation should be documented explicitly. Ideally should be a property on a workflow step associated with the software doing the processing.</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -13437,6 +14231,22 @@
       <c r="K82" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Image Processing Methods Applied' , schema.value</t>
+        </is>
+      </c>
+      <c r="M82" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O82" s="9" t="n"/>
@@ -13546,7 +14356,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="131.15" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>Specimen Thickness Determination Method</t>
@@ -13598,6 +14408,18 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="L83" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Specimen Thickness Determination Method' , schema.value</t>
+        </is>
+      </c>
+      <c r="M83" s="1" t="n"/>
+      <c r="N83" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
+        </is>
+      </c>
       <c r="O83" s="9" t="n"/>
       <c r="P83" s="1" t="inlineStr">
         <is>
@@ -13705,7 +14527,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="n"/>
@@ -13717,6 +14539,9 @@
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
+      <c r="L84" s="1" t="n"/>
+      <c r="M84" s="1" t="n"/>
+      <c r="N84" s="1" t="n"/>
       <c r="O84" s="9" t="n"/>
       <c r="P84" s="1" t="n"/>
       <c r="Q84" s="1" t="n"/>
@@ -13772,7 +14597,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1" ht="43.75" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>6. Quality Control &amp; Uncertainty</t>
@@ -13800,6 +14625,9 @@
           <t>N</t>
         </is>
       </c>
+      <c r="L85" s="1" t="n"/>
+      <c r="M85" s="1" t="n"/>
+      <c r="N85" s="1" t="n"/>
       <c r="O85" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -13911,7 +14739,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="131.15" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>EDS Calibration Standard(s)</t>
@@ -13965,6 +14793,23 @@
       <c r="K86" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:edsCalibrationStandard</t>
+        </is>
+      </c>
+      <c r="M86" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t>property:edsCalibrationStandard
+ dataType: string 
+read-Only: False</t>
         </is>
       </c>
       <c r="O86" s="9" t="n"/>
@@ -14074,7 +14919,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="138.9" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Calibration</t>
@@ -14128,6 +14973,22 @@
       <c r="K87" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Calibration' , schema.value</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N87" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O87" s="9" t="n"/>
@@ -14237,7 +15098,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="145.75" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>Diffraction Calibration Reference</t>
@@ -14291,6 +15152,22 @@
       <c r="K88" s="8" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="L88" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Diffraction Calibration Reference'</t>
+        </is>
+      </c>
+      <c r="M88" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
+        </is>
+      </c>
+      <c r="N88" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O88" s="9" t="n"/>
@@ -14400,7 +15277,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1" ht="87.45" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>EDS Detection Limit</t>
@@ -14454,6 +15331,22 @@
       <c r="K89" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Detection Limit' </t>
+        </is>
+      </c>
+      <c r="M89" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O89" s="9" t="n"/>
@@ -14563,7 +15456,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="67.75" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>EDS Counting Statistics / Accumulation Criterion</t>
@@ -14617,6 +15510,22 @@
       <c r="K90" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L90" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Counting Statistics / Accumulation Criterion' , schema.value</t>
+        </is>
+      </c>
+      <c r="M90" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists  ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N90" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O90" s="9" t="n"/>
@@ -14726,7 +15635,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="1" ht="57.9" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>EDS Dead Time</t>
@@ -14782,19 +15691,19 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Match. Method-level parameter</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>analyteColumn : edsDeadTime 
+      <c r="L91" s="1" t="inlineStr">
+        <is>
+          <t>$Dataset.ada:edsDeadTime</t>
+        </is>
+      </c>
+      <c r="M91" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>property : edsDeadTime 
   datatype: text
   readOnly:true</t>
         </is>
@@ -14906,7 +15815,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1" ht="107.6" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>EELS Sensitivity and Detection Limit</t>
@@ -14960,6 +15869,22 @@
       <c r="K92" s="13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Sensitivity and Detection Limit' , schema.value</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
+        </is>
+      </c>
+      <c r="N92" s="1" t="inlineStr">
+        <is>
+          <t>datatype: string
+read-only: False</t>
         </is>
       </c>
       <c r="O92" s="9" t="n"/>
@@ -15069,7 +15994,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="1" ht="107.6" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>Additional Notes</t>
@@ -15121,21 +16046,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L93" s="1" t="inlineStr">
         <is>
           <t>$.schema:description</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M93" s="1" t="inlineStr">
         <is>
           <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N93" s="1" t="inlineStr">
         <is>
           <t>method property : description
   datatype: text
-  readOnly:false</t>
+  readOnly: false</t>
         </is>
       </c>
       <c r="O93" s="9" t="n"/>
@@ -15246,6 +16171,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:N93">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Editable"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15257,7 +16189,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -15265,7 +16197,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.9" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Protocol-Level Tier</t>
@@ -15287,7 +16219,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="72.90000000000001" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Basic</t>
@@ -15309,7 +16241,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="72.90000000000001" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -15331,7 +16263,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="43.75" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -15353,7 +16285,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="29.15" customHeight="1">
       <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -15365,7 +16297,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.9" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Mode Column</t>

--- a/docs/TEM_TAPP_v7.xlsx
+++ b/docs/TEM_TAPP_v7.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="94" yWindow="1509" windowWidth="21849" windowHeight="9951" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAPP'!$C$1:$N$93</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,56 +27,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="11"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF7030A0"/>
-      <sz val="11"/>
+      <color rgb="007030A0"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF375623"/>
-      <sz val="11"/>
+      <color rgb="00375623"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -89,27 +68,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -187,15 +166,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -554,32 +527,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AJ93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15.3046875" customWidth="1" style="21" min="1" max="1"/>
-    <col width="32.921875" customWidth="1" style="21" min="2" max="2"/>
-    <col width="10.23046875" customWidth="1" style="21" min="3" max="3"/>
-    <col width="9.61328125" customWidth="1" style="21" min="4" max="4"/>
-    <col width="12.23046875" customWidth="1" style="21" min="5" max="5"/>
-    <col width="27.3828125" customWidth="1" style="21" min="6" max="6"/>
-    <col width="10.84375" customWidth="1" style="21" min="7" max="7"/>
-    <col hidden="1" width="14" customWidth="1" style="21" min="8" max="8"/>
-    <col width="8.3046875" customWidth="1" style="21" min="9" max="9"/>
-    <col width="7.765625" customWidth="1" style="21" min="10" max="10"/>
-    <col width="10.4609375" customWidth="1" style="21" min="11" max="11"/>
-    <col width="24.53515625" customWidth="1" style="21" min="12" max="12"/>
-    <col width="23.61328125" customWidth="1" style="21" min="13" max="13"/>
-    <col width="27" customWidth="1" style="21" min="14" max="14"/>
-    <col width="30" customWidth="1" style="21" min="15" max="33"/>
-    <col width="9.23046875" customWidth="1" style="21" min="34" max="16384"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.55" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metadata Item</t>
@@ -635,17 +625,17 @@
           <t>Electron Diffraction</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>schema path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>matchComment</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>implementation notes</t>
         </is>
@@ -761,7 +751,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="19.3" customHeight="1">
+    <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>1. Protocol Identification</t>
@@ -789,9 +779,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
       <c r="O2" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -903,7 +890,7 @@
         </is>
       </c>
     </row>
-    <row r="3" hidden="1" ht="72.90000000000001" customHeight="1">
+    <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Protocol Name</t>
@@ -955,17 +942,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:name</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:name is the short descriptive name for the method.</t>
         </is>
       </c>
-      <c r="N3" s="1" t="n"/>
       <c r="O3" s="9" t="n"/>
       <c r="P3" s="1" t="inlineStr">
         <is>
@@ -1073,7 +1059,7 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" ht="63.45" customHeight="1">
+    <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Technique</t>
@@ -1125,17 +1111,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:measurementTechnique.schema:DefinedTerm.schema:termCode</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:measurementTechnique is a DefinedTerm; use .schema:termCode for the controlled-list code</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>schema:DefinedTerm.schema:termCode
 datatype: string
@@ -1250,7 +1236,7 @@
         </is>
       </c>
     </row>
-    <row r="5" hidden="1" ht="87.45" customHeight="1">
+    <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Protocol Author</t>
@@ -1302,17 +1288,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:creator.schema:Person | schema.Organization.schema:name</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>match. schema:creator is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Read-only: True
 DataType: string</t>
@@ -1425,7 +1411,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="78.55" customHeight="1">
+    <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Laboratory</t>
@@ -1477,17 +1463,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:location.scheme:Place.schema:name</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>match. ada:laboratory extends spatialExtent (schema:Place); schema:name is the lab/facility name.</t>
         </is>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Read-only: False
 DataType: string</t>
@@ -1600,7 +1586,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58.3" customHeight="1">
+    <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Laboratory ID</t>
@@ -1652,17 +1638,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:location.scheme:Place.schema:identifier</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>match. schema:Place schema:identifier (ROR or other PID) on ada:laboratory.</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Read-only: False
 DataType: string  format: uri</t>
@@ -1775,7 +1761,7 @@
         </is>
       </c>
     </row>
-    <row r="8" hidden="1" ht="102" customHeight="1">
+    <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Protocol Start Date</t>
@@ -1827,17 +1813,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:datePublished</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>match. methodDefinition.schema:datePublished is explicitly described as 'ISO 8601 date when this method configuration was first used'.</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Read-only: True
 DataType: Date</t>
@@ -1950,7 +1936,7 @@
         </is>
       </c>
     </row>
-    <row r="9" hidden="1" ht="145.75" customHeight="1">
+    <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Protocol Development</t>
@@ -2002,17 +1988,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:funding[].schema:MonetaryGrant.schema:name</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>schema:funding[] is an array of MonetaryGrant; also has schema:identifier (award number) and schema:funder (organisation). put text in MonetaryGrant name unless can clearly parse identifier distinct from name.</t>
         </is>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>read-only:True</t>
         </is>
@@ -2124,7 +2110,7 @@
         </is>
       </c>
     </row>
-    <row r="10" hidden="1" ht="131.15" customHeight="1">
+    <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Protocol Reference(s)</t>
@@ -2176,17 +2162,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'techniquePublication'].</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>schema:relatedLink[] is a labeledLink with schema:url and schema:name; fits DOIs/URLs of method publications. target URL to publication , target name should be title of publication</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>read-only:True</t>
         </is>
@@ -2298,7 +2284,7 @@
         </is>
       </c>
     </row>
-    <row r="11" hidden="1" ht="65.15000000000001" customHeight="1">
+    <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Protocol DOI</t>
@@ -2350,17 +2336,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>$Dataset.schema:measuremntTechnique.schema:DefinedTerm.schema.name and schema.identifier</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>This should be the identifier for the protocol definition that the analysis level 'detail' is extenting for a particular dataset.</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
@@ -2472,7 +2458,7 @@
         </is>
       </c>
     </row>
-    <row r="12" hidden="1" ht="102" customHeight="1">
+    <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Analyst</t>
@@ -2524,13 +2510,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:Agent/schema:Person.schema:name, schema:identifier</t>
         </is>
       </c>
-      <c r="M12" s="1" t="n"/>
-      <c r="N12" s="1" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -2638,7 +2622,7 @@
         </is>
       </c>
     </row>
-    <row r="13" hidden="1" ht="29.15" customHeight="1">
+    <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Analysis Start Date</t>
@@ -2690,13 +2674,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:startDate</t>
         </is>
       </c>
-      <c r="M13" s="1" t="n"/>
-      <c r="N13" s="1" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="1" t="inlineStr">
         <is>
@@ -2804,7 +2786,7 @@
         </is>
       </c>
     </row>
-    <row r="14" hidden="1" ht="43.75" customHeight="1">
+    <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Analysis End Date</t>
@@ -2856,13 +2838,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:endDate</t>
         </is>
       </c>
-      <c r="M14" s="1" t="n"/>
-      <c r="N14" s="1" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="1" t="inlineStr">
         <is>
@@ -2970,7 +2950,7 @@
         </is>
       </c>
     </row>
-    <row r="15" hidden="1" ht="41.25" customHeight="1">
+    <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Funding Source for Analysis</t>
@@ -3022,13 +3002,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>$Dataset.schema:funding</t>
         </is>
       </c>
-      <c r="M15" s="1" t="n"/>
-      <c r="N15" s="1" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="1" t="inlineStr">
         <is>
@@ -3136,7 +3114,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="79.84999999999999" customHeight="1">
+    <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Coupled Technique(s)</t>
@@ -3188,17 +3166,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:name</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>range should be analytical technique vocabulary</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -3311,7 +3289,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="131.25" customHeight="1">
+    <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Coupling Description</t>
@@ -3363,17 +3341,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:description</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>text description of relationship</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -3486,7 +3464,7 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1" ht="72.90000000000001" customHeight="1">
+    <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Coupled Protocol DOI</t>
@@ -3538,13 +3516,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:url</t>
         </is>
       </c>
-      <c r="M18" s="1" t="n"/>
-      <c r="N18" s="1" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="1" t="inlineStr">
         <is>
@@ -3652,7 +3628,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" ht="116.6" customHeight="1">
+    <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Coupled Dataset or Publication Reference</t>
@@ -3704,13 +3680,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledDataset'].schema:target</t>
         </is>
       </c>
-      <c r="M19" s="1" t="n"/>
-      <c r="N19" s="1" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
@@ -3818,7 +3792,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
@@ -3830,9 +3804,6 @@
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="1" t="n"/>
-      <c r="M20" s="1" t="n"/>
-      <c r="N20" s="1" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="1" t="n"/>
       <c r="Q20" s="1" t="n"/>
@@ -3888,7 +3859,7 @@
         </is>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2. Samples</t>
@@ -3916,9 +3887,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L21" s="1" t="n"/>
-      <c r="M21" s="1" t="n"/>
-      <c r="N21" s="1" t="n"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4030,7 +3998,7 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" ht="121.3" customHeight="1">
+    <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Target Material</t>
@@ -4082,17 +4050,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:object[].schema:DefinedTerm.schema.name</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>match. schema:object[] is an array of DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary or target materials…</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>schema:DefinedTerm.schema:termCode
 datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify}
@@ -4206,7 +4174,7 @@
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" ht="204" customHeight="1">
+    <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Sample Preparation Method</t>
@@ -4258,17 +4226,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:additionalType='samplePreparation'].schema:name</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Sample preparation is a dedicated step (typically schema:position=1) in the actionProcess; schema:object is input, mostly likely the original sample. Schema:result is the product that will be used directly for analysis, e.g. polished thin section or epoxy mount; describe procedure in schema:step/schema:description</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>property:samplePreparationMethod
  dataType: string 
@@ -4383,7 +4351,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="169.3" customHeight="1">
+    <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Sample Preparation Details</t>
@@ -4435,13 +4403,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:additionalType='samplePreparation'].schema:description</t>
         </is>
       </c>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -4554,7 +4521,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" ht="114" customHeight="1">
+    <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Sample Name</t>
@@ -4606,13 +4573,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:object[@type ="schema:Thing",            "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:name</t>
         </is>
       </c>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="1" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="1" t="inlineStr">
         <is>
@@ -4720,7 +4685,7 @@
         </is>
       </c>
     </row>
-    <row r="26" hidden="1" ht="102" customHeight="1">
+    <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Sample Persistent Identifier</t>
@@ -4772,13 +4737,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:identifier</t>
         </is>
       </c>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="1" t="n"/>
       <c r="O26" s="9" t="n"/>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -4886,7 +4849,7 @@
         </is>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
@@ -4898,9 +4861,6 @@
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="n"/>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="1" t="n"/>
       <c r="Q27" s="1" t="n"/>
@@ -4956,7 +4916,7 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" ht="29.15" customHeight="1">
+    <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>3. Instrument &amp; Software</t>
@@ -4984,9 +4944,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="1" t="n"/>
       <c r="O28" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -5098,7 +5055,7 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" ht="87.45" customHeight="1">
+    <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Instrument Manufacturer</t>
@@ -5150,17 +5107,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name</t>
         </is>
       </c>
-      <c r="M29" s="1" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>match. CDIF instrument inherits schema.org Product's schema:manufacturer.</t>
         </is>
       </c>
-      <c r="N29" s="1" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>read-only: True
 dataType: string
@@ -5274,7 +5231,7 @@
         </is>
       </c>
     </row>
-    <row r="30" hidden="1" ht="87.45" customHeight="1">
+    <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Instrument Model</t>
@@ -5326,17 +5283,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:model.schema:name</t>
         </is>
       </c>
-      <c r="M30" s="1" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>match. CDIF instrument inherits schema.org Product's schema:model.</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>READ-only: irue
 dataType: string</t>
@@ -5449,7 +5406,7 @@
         </is>
       </c>
     </row>
-    <row r="31" hidden="1" ht="145.75" customHeight="1">
+    <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Electron Source</t>
@@ -5501,17 +5458,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ElectronSource'].schema:name</t>
         </is>
       </c>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>match. Electron source/gun modelled as a sub-component of the instrument via schema:hasPart[]; classify the part via schema:additionalType (e.g. 'ElectronGun:FEG') and carry the label in schema:name.</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>read-only: True
 dataType: string
@@ -5625,7 +5582,7 @@
         </is>
       </c>
     </row>
-    <row r="32" hidden="1" ht="94.75" customHeight="1">
+    <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Aberration Corrector</t>
@@ -5677,13 +5634,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'AberrationCorrector'].schema:name</t>
         </is>
       </c>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>read-only: True
 dataType: string
@@ -5797,7 +5753,7 @@
         </is>
       </c>
     </row>
-    <row r="33" hidden="1" ht="72.90000000000001" customHeight="1">
+    <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Monochromator</t>
@@ -5853,17 +5809,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L33" s="1" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'Monochromator'].schema:name</t>
         </is>
       </c>
-      <c r="M33" s="1" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N33" s="1" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>read-only: True
 dataType: string
@@ -5977,7 +5933,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="87.45" customHeight="1">
+    <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Sample Holder</t>
@@ -6029,13 +5985,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L34" s="1" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'SampleHolder'].schema:name</t>
         </is>
       </c>
-      <c r="M34" s="1" t="n"/>
-      <c r="N34" s="1" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>read-only: False
 dataType: string
@@ -6149,7 +6104,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="66.90000000000001" customHeight="1">
+    <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Spectroscopic Detector(s)</t>
@@ -6205,17 +6160,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L35" s="1" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'SpectroscopicDetector'].schema:name</t>
         </is>
       </c>
-      <c r="M35" s="1" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N35" s="1" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>read-only: False
 dataType: string
@@ -6329,7 +6284,7 @@
         </is>
       </c>
     </row>
-    <row r="36" hidden="1" ht="174.9" customHeight="1">
+    <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>EDS Detector Configuration</t>
@@ -6385,18 +6340,18 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L36" s="1" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'edsDetector']</t>
         </is>
       </c>
-      <c r="M36" s="1" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'
 Match as sub-component. EDS detector as a hasPart with schema:manufacturer, schema:model, and schema:description</t>
         </is>
       </c>
-      <c r="N36" s="1" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>read-only: True
 dataType: string</t>
@@ -6509,7 +6464,7 @@
         </is>
       </c>
     </row>
-    <row r="37" hidden="1" ht="160.3" customHeight="1">
+    <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>EELS Spectrometer</t>
@@ -6565,17 +6520,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L37" s="1" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'eelsSpectrometer']</t>
         </is>
       </c>
-      <c r="M37" s="1" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N37" s="1" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Read-only: True
 dataType: string</t>
@@ -6688,7 +6643,7 @@
         </is>
       </c>
     </row>
-    <row r="38" hidden="1" ht="102" customHeight="1">
+    <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Imaging and Diffraction Detectors</t>
@@ -6740,13 +6695,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ImagingAndDiffractionDetector']</t>
         </is>
       </c>
-      <c r="M38" s="1" t="n"/>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Read-only: True
 dataType: string</t>
@@ -6859,7 +6813,7 @@
         </is>
       </c>
     </row>
-    <row r="39" hidden="1" ht="114.9" customHeight="1">
+    <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Detector</t>
@@ -6915,17 +6869,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'STEM4Ddetector']</t>
         </is>
       </c>
-      <c r="M39" s="1" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Read-only: True
 dataType: string</t>
@@ -7038,7 +6992,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="68.15000000000001" customHeight="1">
+    <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Acquisition Software</t>
@@ -7090,17 +7044,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>$MethodDefinition.bios:computationalTool[]</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
         </is>
       </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>toolRole = acquisition
 read-only: False
@@ -7214,7 +7168,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="59.6" customHeight="1">
+    <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>SAED Pattern Simulation Software</t>
@@ -7270,17 +7224,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" s="1" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>$MethodDefinition.bios:computationalTool[]</t>
         </is>
       </c>
-      <c r="M41" s="1" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N41" s="1" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>toolRole = processing
 read-only: False
@@ -7394,7 +7348,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="131.15" customHeight="1">
+    <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>Data Reduction Software</t>
@@ -7446,17 +7400,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>$MethodDefinition.bios:computationalTool[]</t>
         </is>
       </c>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>toolRole = data reduction
 read-only: False
@@ -7570,7 +7524,7 @@
         </is>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
@@ -7582,9 +7536,6 @@
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="1" t="n"/>
-      <c r="M43" s="1" t="n"/>
-      <c r="N43" s="1" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="n"/>
@@ -7640,7 +7591,7 @@
         </is>
       </c>
     </row>
-    <row r="44" hidden="1" ht="29.15" customHeight="1">
+    <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>4. Measurement Information</t>
@@ -7668,9 +7619,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L44" s="1" t="n"/>
-      <c r="M44" s="1" t="n"/>
-      <c r="N44" s="1" t="n"/>
       <c r="O44" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -7782,7 +7730,7 @@
         </is>
       </c>
     </row>
-    <row r="45" hidden="1" ht="63" customHeight="1">
+    <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Analytical Mode</t>
@@ -7808,9 +7756,9 @@
           <t>Controlled vocabulary</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>TEM Imaging' | 'STEM Imaging' | 'Electron Diffraction' | 'STEM Imaging; Electron Diffraction'</t>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>'TEM Imaging' | 'STEM Imaging' | 'Electron Diffraction' | 'STEM Imaging; Electron Diffraction'</t>
         </is>
       </c>
       <c r="G45" s="1" t="n"/>
@@ -7834,13 +7782,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L45" s="1" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:analyticalMode[]</t>
         </is>
       </c>
-      <c r="M45" s="1" t="n"/>
-      <c r="N45" s="1" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>property:analyticalMode
  dataType: string 
@@ -7875,7 +7822,7 @@
       <c r="AI45" s="1" t="n"/>
       <c r="AJ45" s="1" t="n"/>
     </row>
-    <row r="46" ht="50.6" customHeight="1">
+    <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>Accelerating Voltage</t>
@@ -7931,17 +7878,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L46" s="1" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:acceleratingVoltage</t>
         </is>
       </c>
-      <c r="M46" s="1" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve"> schema:unitText='kV'</t>
         </is>
       </c>
-      <c r="N46" s="1" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">property:  acceleratingVoltage
   datatype: string
@@ -8056,7 +8003,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="121.3" customHeight="1">
+    <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Analytical Sub-mode</t>
@@ -8108,17 +8055,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L47" s="1" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:analyticalMode[]</t>
         </is>
       </c>
-      <c r="M47" s="1" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>add to analyticalMode list.</t>
         </is>
       </c>
-      <c r="N47" s="1" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>property:analyticalMode
  dataType: string 
@@ -8233,7 +8180,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="116.6" customHeight="1">
+    <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>TEM Objective Aperture</t>
@@ -8289,17 +8236,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L48" s="1" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'TEM Objective Aperture',  schema.value</t>
         </is>
       </c>
-      <c r="M48" s="1" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'</t>
         </is>
       </c>
-      <c r="N48" s="1" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -8412,7 +8359,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="87.45" customHeight="1">
+    <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>EFTEM Energy Window</t>
@@ -8468,17 +8415,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L49" s="1" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EFTEM Energy Window'  , schema.value</t>
         </is>
       </c>
-      <c r="M49" s="1" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'</t>
         </is>
       </c>
-      <c r="N49" s="1" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -8591,7 +8538,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="61.3" customHeight="1">
+    <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>HAADF Collection Angles</t>
@@ -8647,17 +8594,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L50" s="1" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'HAADF Collection Angles' , schema.value</t>
         </is>
       </c>
-      <c r="M50" s="1" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N50" s="1" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -8770,7 +8717,7 @@
         </is>
       </c>
     </row>
-    <row r="51" hidden="1" ht="79.75" customHeight="1">
+    <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>Convergence Semi-Angle</t>
@@ -8826,17 +8773,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L51" s="1" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:convergenceSemiAngle</t>
         </is>
       </c>
-      <c r="M51" s="1" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'  or ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N51" s="1" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>property: convergenceSemiAngle datatype: string readOnly: True</t>
         </is>
@@ -8948,7 +8895,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="71.15000000000001" customHeight="1">
+    <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>STEM Probe Diameter</t>
@@ -9004,17 +8951,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L52" s="1" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Probe Diameter' , schema.value</t>
         </is>
       </c>
-      <c r="M52" s="1" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N52" s="1" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -9127,7 +9074,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="87.45" customHeight="1">
+    <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>STEM Probe Current</t>
@@ -9183,17 +9130,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L53" s="1" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Probe Current' , schema.value</t>
         </is>
       </c>
-      <c r="M53" s="1" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N53" s="1" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -9306,7 +9253,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="56.15" customHeight="1">
+    <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>STEM Dwell Time per Pixel</t>
@@ -9362,17 +9309,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L54" s="1" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:stemDwellTimePerPixel</t>
         </is>
       </c>
-      <c r="M54" s="1" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N54" s="1" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>property:stemDwellTimePerPixel
  dataType: string 
@@ -9486,7 +9433,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="58.3" customHeight="1">
+    <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>STEM Scan Dimensions</t>
@@ -9542,17 +9489,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L55" s="1" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Scan Dimensions' , schema.value</t>
         </is>
       </c>
-      <c r="M55" s="1" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N55" s="1" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -9665,7 +9612,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="72.90000000000001" customHeight="1">
+    <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>STEM Frame Averaging</t>
@@ -9721,17 +9668,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L56" s="1" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'STEM Frame Averaging' , schema.value</t>
         </is>
       </c>
-      <c r="M56" s="1" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N56" s="1" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -9844,7 +9791,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="56.6" customHeight="1">
+    <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>Camera Length</t>
@@ -9900,17 +9847,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L57" s="1" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:cameraLength</t>
         </is>
       </c>
-      <c r="M57" s="1" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'STEM Imaging'  or ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N57" s="1" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>property:cameraLength
  dataType: string 
@@ -10024,7 +9971,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="72.90000000000001" customHeight="1">
+    <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Selected-Area Aperture Size</t>
@@ -10080,17 +10027,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L58" s="1" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Selected-Area Aperture Size' , schema.value</t>
         </is>
       </c>
-      <c r="M58" s="1" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N58" s="1" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -10203,7 +10150,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="53.6" customHeight="1">
+    <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>Precession Angle</t>
@@ -10259,17 +10206,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L59" s="1" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Precession Angle' , schema.value</t>
         </is>
       </c>
-      <c r="M59" s="1" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N59" s="1" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -10382,7 +10329,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="72.90000000000001" customHeight="1">
+    <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Scan Grid and Area</t>
@@ -10438,17 +10385,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L60" s="1" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Scan Grid and Area' , schema.value</t>
         </is>
       </c>
-      <c r="M60" s="1" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N60" s="1" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -10561,7 +10508,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="50.15" customHeight="1">
+    <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Dwell Time per Probe Position</t>
@@ -10617,17 +10564,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L61" s="1" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Dwell Time per Probe Position' , schema.value</t>
         </is>
       </c>
-      <c r="M61" s="1" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N61" s="1" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -10740,7 +10687,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="131.15" customHeight="1">
+    <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Diffraction Camera Length Calibration Method</t>
@@ -10796,17 +10743,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L62" s="1" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Diffraction Camera Length Calibration Method' , schema.value</t>
         </is>
       </c>
-      <c r="M62" s="1" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N62" s="1" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -10919,7 +10866,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="72" customHeight="1">
+    <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>EDS Acquisition Mode</t>
@@ -10975,17 +10922,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L63" s="1" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:edsAcquisitionMode</t>
         </is>
       </c>
-      <c r="M63" s="1" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N63" s="1" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>property:edsAcquisitionMode
  dataType: string 
@@ -11100,7 +11047,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="53.6" customHeight="1">
+    <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>EDS Live Time per Point or Pixel</t>
@@ -11156,17 +11103,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L64" s="1" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Live Time per Point or Pixel' , schema.value</t>
         </is>
       </c>
-      <c r="M64" s="1" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N64" s="1" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -11279,7 +11226,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="72.90000000000001" customHeight="1">
+    <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>EDS Energy Range</t>
@@ -11335,17 +11282,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L65" s="1" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Energy Range' , schema.value</t>
         </is>
       </c>
-      <c r="M65" s="1" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N65" s="1" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -11458,7 +11405,7 @@
         </is>
       </c>
     </row>
-    <row r="66" hidden="1" ht="96" customHeight="1">
+    <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>EDS Quantification Method</t>
@@ -11514,17 +11461,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L66" s="1" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:edsQuantificationMethod</t>
         </is>
       </c>
-      <c r="M66" s="1" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N66" s="1" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>property:edsQuantificationMethod
  dataType: string 
@@ -11639,7 +11586,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
+    <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>Analyte</t>
@@ -11695,17 +11642,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L67" s="1" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>special handling</t>
         </is>
       </c>
-      <c r="M67" s="1" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N67" s="1" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">use to generate the default analytes list using the analyteTemplate; </t>
         </is>
@@ -11817,7 +11764,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="88.75" customHeight="1">
+    <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>EELS Acquisition Mode</t>
@@ -11873,17 +11820,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L68" s="1" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:eelsAcquisitionMode</t>
         </is>
       </c>
-      <c r="M68" s="1" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N68" s="1" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>property:eelsAcquisitionMode
  dataType: string 
@@ -11998,7 +11945,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="81" customHeight="1">
+    <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>EELS Edges</t>
@@ -12054,17 +12001,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L69" s="1" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:eelsEdges[]</t>
         </is>
       </c>
-      <c r="M69" s="1" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N69" s="1" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>property:eelsEdges
  dataType: list of string 
@@ -12178,7 +12125,7 @@
         </is>
       </c>
     </row>
-    <row r="70" hidden="1" ht="72.90000000000001" customHeight="1">
+    <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>EELS Collection Semi-Angle</t>
@@ -12234,17 +12181,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L70" s="1" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:eelsCollectionSemiAngle</t>
         </is>
       </c>
-      <c r="M70" s="1" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N70" s="1" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>property:eelsCollectionSemiAngle
  dataType: string 
@@ -12358,7 +12305,7 @@
         </is>
       </c>
     </row>
-    <row r="71" hidden="1" ht="58.3" customHeight="1">
+    <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Dispersion</t>
@@ -12414,17 +12361,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L71" s="1" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Dispersion' , schema.value</t>
         </is>
       </c>
-      <c r="M71" s="1" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N71" s="1" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: True</t>
@@ -12537,7 +12484,7 @@
         </is>
       </c>
     </row>
-    <row r="72" hidden="1" ht="67.3" customHeight="1">
+    <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Resolution</t>
@@ -12593,17 +12540,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L72" s="1" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Resolution' , schema.value</t>
         </is>
       </c>
-      <c r="M72" s="1" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N72" s="1" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: True</t>
@@ -12716,7 +12663,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="72.90000000000001" customHeight="1">
+    <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>EELS Acquisition Time per Spectrum</t>
@@ -12772,17 +12719,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L73" s="1" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:eelsAcquisitionTimePerSpectrum</t>
         </is>
       </c>
-      <c r="M73" s="1" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N73" s="1" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>property:eelsAcquisitionTimePerSpectrum
  dataType: string 
@@ -12896,7 +12843,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="87.45" customHeight="1">
+    <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Loss Range</t>
@@ -12952,17 +12899,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L74" s="1" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:eelsEnergyLossRange</t>
         </is>
       </c>
-      <c r="M74" s="1" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N74" s="1" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>property:eelsEnergyLossRange
  dataType: string 
@@ -13076,7 +13023,7 @@
         </is>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="n"/>
@@ -13088,9 +13035,6 @@
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
-      <c r="L75" s="1" t="n"/>
-      <c r="M75" s="1" t="n"/>
-      <c r="N75" s="1" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="1" t="n"/>
       <c r="Q75" s="1" t="n"/>
@@ -13146,7 +13090,7 @@
         </is>
       </c>
     </row>
-    <row r="76" hidden="1" ht="29.15" customHeight="1">
+    <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>5. Data Processing</t>
@@ -13174,9 +13118,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L76" s="1" t="n"/>
-      <c r="M76" s="1" t="n"/>
-      <c r="N76" s="1" t="n"/>
       <c r="O76" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -13288,7 +13229,7 @@
         </is>
       </c>
     </row>
-    <row r="77" hidden="1" ht="102" customHeight="1">
+    <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>Phase Identification Method</t>
@@ -13340,13 +13281,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L77" s="1" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:phaseIdentificatonMethod</t>
         </is>
       </c>
-      <c r="M77" s="1" t="n"/>
-      <c r="N77" s="1" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>property:phaseIdentificatonMethod
  dataType: string 
@@ -13461,7 +13401,7 @@
         </is>
       </c>
     </row>
-    <row r="78" hidden="1" ht="102" customHeight="1">
+    <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>4D-STEM Orientation Mapping Method</t>
@@ -13517,17 +13457,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L78" s="1" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'4D-STEM Orientation Mapping Method' , schema.value</t>
         </is>
       </c>
-      <c r="M78" s="1" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N78" s="1" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: True</t>
@@ -13640,7 +13580,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="72.90000000000001" customHeight="1">
+    <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>EELS Background Subtraction Method</t>
@@ -13696,17 +13636,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L79" s="1" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Background Subtraction Method' , schema.value</t>
         </is>
       </c>
-      <c r="M79" s="1" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N79" s="1" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -13819,7 +13759,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="87.45" customHeight="1">
+    <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>EELS Plural Scattering Correction</t>
@@ -13875,17 +13815,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Plural Scattering Correction' , schema.value</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -13998,7 +13938,7 @@
         </is>
       </c>
     </row>
-    <row r="81" hidden="1" ht="174.9" customHeight="1">
+    <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>EDS Spectral Processing Type</t>
@@ -14006,7 +13946,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Method used to process EDS spectra and extract net peak intensities from raw spectral data. Applied before quantification (EDS Quantification Method). Common approaches include background fitting and subtraction followed by peak integration, and filter fit or Gaussian deconvolution for overlapping peaks. Ideally should be a property on a workflow step associated with the software doing the processing.</t>
+          <t>Method used to process EDS spectra and extract net peak intensities from raw spectral data. Applied before quantification (EDS Quantification Method). Common approaches include background fitting and subtraction followed by peak integration, and filter fit or Gaussian deconvolution for overlapping peaks.</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -14054,17 +13994,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L81" s="1" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Spectral Processing Type' , schema.value</t>
         </is>
       </c>
-      <c r="M81" s="1" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N81" s="1" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: True</t>
@@ -14177,7 +14117,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="116.6" customHeight="1">
+    <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Image Processing Methods Applied</t>
@@ -14185,7 +14125,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Image processing steps applied to TEM or STEM images during or after acquisition. Non-linear processing steps that could affect quantitative interpretation should be documented explicitly. Ideally should be a property on a workflow step associated with the software doing the processing.</t>
+          <t>Image processing steps applied to TEM or STEM images during or after acquisition. Non-linear processing steps that could affect quantitative interpretation should be documented explicitly.</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -14233,17 +14173,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L82" s="1" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Image Processing Methods Applied' , schema.value</t>
         </is>
       </c>
-      <c r="M82" s="1" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N82" s="1" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -14356,7 +14296,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="131.15" customHeight="1">
+    <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>Specimen Thickness Determination Method</t>
@@ -14408,13 +14348,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L83" s="1" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Specimen Thickness Determination Method' , schema.value</t>
         </is>
       </c>
-      <c r="M83" s="1" t="n"/>
-      <c r="N83" s="1" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -14527,7 +14466,7 @@
         </is>
       </c>
     </row>
-    <row r="84" hidden="1">
+    <row r="84">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="n"/>
@@ -14539,9 +14478,6 @@
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
-      <c r="L84" s="1" t="n"/>
-      <c r="M84" s="1" t="n"/>
-      <c r="N84" s="1" t="n"/>
       <c r="O84" s="9" t="n"/>
       <c r="P84" s="1" t="n"/>
       <c r="Q84" s="1" t="n"/>
@@ -14597,7 +14533,7 @@
         </is>
       </c>
     </row>
-    <row r="85" hidden="1" ht="43.75" customHeight="1">
+    <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>6. Quality Control &amp; Uncertainty</t>
@@ -14625,9 +14561,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L85" s="1" t="n"/>
-      <c r="M85" s="1" t="n"/>
-      <c r="N85" s="1" t="n"/>
       <c r="O85" s="5" t="inlineStr">
         <is>
           <t>N</t>
@@ -14739,7 +14672,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="131.15" customHeight="1">
+    <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>EDS Calibration Standard(s)</t>
@@ -14795,17 +14728,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L86" s="1" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>$MethodDefinition.ada:edsCalibrationStandard</t>
         </is>
       </c>
-      <c r="M86" s="1" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N86" s="1" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>property:edsCalibrationStandard
  dataType: string 
@@ -14919,7 +14852,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="138.9" customHeight="1">
+    <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>EELS Energy Calibration</t>
@@ -14975,17 +14908,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L87" s="1" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Energy Calibration' , schema.value</t>
         </is>
       </c>
-      <c r="M87" s="1" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N87" s="1" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -15098,7 +15031,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="145.75" customHeight="1">
+    <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>Diffraction Calibration Reference</t>
@@ -15154,17 +15087,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L88" s="1" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'Diffraction Calibration Reference'</t>
         </is>
       </c>
-      <c r="M88" s="1" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'Electron Diffraction'</t>
         </is>
       </c>
-      <c r="N88" s="1" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -15277,7 +15210,7 @@
         </is>
       </c>
     </row>
-    <row r="89" hidden="1" ht="87.45" customHeight="1">
+    <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>EDS Detection Limit</t>
@@ -15333,17 +15266,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L89" s="1" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Detection Limit' </t>
         </is>
       </c>
-      <c r="M89" s="1" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N89" s="1" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -15456,7 +15389,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="67.75" customHeight="1">
+    <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>EDS Counting Statistics / Accumulation Criterion</t>
@@ -15512,17 +15445,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L90" s="1" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EDS Counting Statistics / Accumulation Criterion' , schema.value</t>
         </is>
       </c>
-      <c r="M90" s="1" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>validation: if exists  ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N90" s="1" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -15635,7 +15568,7 @@
         </is>
       </c>
     </row>
-    <row r="91" hidden="1" ht="57.9" customHeight="1">
+    <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>EDS Dead Time</t>
@@ -15691,17 +15624,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L91" s="1" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>$Dataset.ada:edsDeadTime</t>
         </is>
       </c>
-      <c r="M91" s="1" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>property : edsDeadTime 
   datatype: text
@@ -15815,7 +15748,7 @@
         </is>
       </c>
     </row>
-    <row r="92" hidden="1" ht="107.6" customHeight="1">
+    <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>EELS Sensitivity and Detection Limit</t>
@@ -15871,17 +15804,17 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L92" s="1" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>$MethodDefinition.schema:additionalProperty[].schema:name:'EELS Sensitivity and Detection Limit' , schema.value</t>
         </is>
       </c>
-      <c r="M92" s="1" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>validation: if exists ada:analyticalMode = 'TEM Imaging'  or ada:analyticalMode = 'STEM Imaging'</t>
         </is>
       </c>
-      <c r="N92" s="1" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>datatype: string
 read-only: False</t>
@@ -15994,7 +15927,7 @@
         </is>
       </c>
     </row>
-    <row r="93" hidden="1" ht="107.6" customHeight="1">
+    <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>Additional Notes</t>
@@ -16046,17 +15979,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L93" s="1" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>$.schema:description</t>
         </is>
       </c>
-      <c r="M93" s="1" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
         </is>
       </c>
-      <c r="N93" s="1" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>method property : description
   datatype: text
@@ -16171,13 +16104,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:N93">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Editable"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16189,7 +16115,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -16197,7 +16123,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.9" customHeight="1">
+    <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Protocol-Level Tier</t>
@@ -16219,7 +16145,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72.90000000000001" customHeight="1">
+    <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Basic</t>
@@ -16241,7 +16167,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="72.90000000000001" customHeight="1">
+    <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -16263,7 +16189,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="43.75" customHeight="1">
+    <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -16285,7 +16211,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.15" customHeight="1">
+    <row r="5">
       <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Advanced</t>
@@ -16297,7 +16223,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.9" customHeight="1">
+    <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Mode Column</t>
